--- a/src/ExcelsiorAspose.Tests/IncludeTests.ToggleBasedOnState.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/IncludeTests.ToggleBasedOnState.verified.xlsx
@@ -476,7 +476,7 @@
     <col min="2" max="2" width="8.71428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14" customHeight="1">
+    <row r="1" spans="1:2" ht="16" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,7 +484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14" customHeight="1">
+    <row r="2" spans="1:2" ht="16" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -492,7 +492,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14" customHeight="1">
+    <row r="3" spans="1:2" ht="16" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>

--- a/src/ExcelsiorAspose.Tests/IncludeTests.ToggleBasedOnState.verified.xlsx
+++ b/src/ExcelsiorAspose.Tests/IncludeTests.ToggleBasedOnState.verified.xlsx
@@ -476,7 +476,7 @@
     <col min="2" max="2" width="8.71428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16" customHeight="1">
+    <row r="1" spans="1:2" ht="14" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -484,7 +484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16" customHeight="1">
+    <row r="2" spans="1:2" ht="14" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -492,7 +492,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16" customHeight="1">
+    <row r="3" spans="1:2" ht="14" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
